--- a/fichiers/math φ - harmonie - 01 - harmonie temporelle/rythmes.xlsx
+++ b/fichiers/math φ - harmonie - 01 - harmonie temporelle/rythmes.xlsx
@@ -429,7 +429,7 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -440,7 +440,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -481,10 +481,10 @@
         <v>clap</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
